--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/03_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/03_NovatedApp_Regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BC2B7-F14E-46C2-96A1-A5D4D62A0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86072938-7D03-4068-9FE3-CE000B372C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="133">
   <si>
     <t>TC ID</t>
   </si>
@@ -131,24 +131,12 @@
     <t>${TC001.Odometer}</t>
   </si>
   <si>
-    <t>Maintenance</t>
-  </si>
-  <si>
     <t>C:\Users\Public\Documents\Invoice.pdf</t>
   </si>
   <si>
     <t>Tax Invoice</t>
   </si>
   <si>
-    <t>12301</t>
-  </si>
-  <si>
-    <t>4 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-652</t>
-  </si>
-  <si>
     <t>End Of Lease Date</t>
   </si>
   <si>
@@ -182,102 +170,198 @@
     <t>TC006</t>
   </si>
   <si>
+    <t>${TC003.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC003.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC003.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>Vehicle General maintenance has been completed</t>
+  </si>
+  <si>
+    <t>22 Apr 2026 04:33 AM</t>
+  </si>
+  <si>
+    <t>Submitted On</t>
+  </si>
+  <si>
+    <t>22 Apr 2026 04:34 AM</t>
+  </si>
+  <si>
+    <t>Updated On</t>
+  </si>
+  <si>
+    <t>${TC005.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC005.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC005.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC005.Odometer}</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Primary Email</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Vehicle Description</t>
+  </si>
+  <si>
+    <t>Registration Number</t>
+  </si>
+  <si>
+    <t>Registration State</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Status1</t>
+  </si>
+  <si>
+    <t>Updated By1</t>
+  </si>
+  <si>
+    <t>Assigned To1</t>
+  </si>
+  <si>
+    <t>$1,000.00</t>
+  </si>
+  <si>
+    <t>22 May 2026</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Toshihiko</t>
+  </si>
+  <si>
+    <t>Inafune</t>
+  </si>
+  <si>
+    <t>inafune@jfcaust.com.au.test</t>
+  </si>
+  <si>
+    <t>0469750861</t>
+  </si>
+  <si>
+    <t>Test Employer</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
+  </si>
+  <si>
+    <t>FTV21M</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Auto Lease</t>
+  </si>
+  <si>
+    <t>01/02/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>${TC003.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Odometer}</t>
+  </si>
+  <si>
+    <t>Insurance Australia Group (IAG)</t>
+  </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>The new australia insurance</t>
+  </si>
+  <si>
+    <t>12350</t>
+  </si>
+  <si>
+    <t>REQ-800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy of CTP Renewal </t>
+  </si>
+  <si>
+    <t>12353</t>
+  </si>
+  <si>
+    <t>REQ-803</t>
+  </si>
+  <si>
+    <t>$2,000.00</t>
+  </si>
+  <si>
+    <t>12355</t>
+  </si>
+  <si>
+    <t>REQ-805</t>
+  </si>
+  <si>
+    <t>Claim type other has been raised due to some spare damage.</t>
+  </si>
+  <si>
     <t>TC007</t>
   </si>
   <si>
     <t>TC008</t>
   </si>
   <si>
-    <t>${TC003.Last Odometer Reading}</t>
-  </si>
-  <si>
-    <t>${TC003.New Odometer}</t>
-  </si>
-  <si>
-    <t>${TC003.Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC003.Last Reading Date}</t>
-  </si>
-  <si>
-    <t>Tyres</t>
-  </si>
-  <si>
-    <t>Vehicle General maintenance has been completed</t>
-  </si>
-  <si>
-    <t>12303</t>
-  </si>
-  <si>
-    <t>REQ-622</t>
-  </si>
-  <si>
-    <t>11/02/2026 11:00 GMT+11:00</t>
-  </si>
-  <si>
-    <t>David Cracknell</t>
-  </si>
-  <si>
-    <t>22 Apr 2026 04:33 AM</t>
-  </si>
-  <si>
-    <t>Submitted On</t>
-  </si>
-  <si>
-    <t>22 Apr 2026 04:34 AM</t>
-  </si>
-  <si>
-    <t>Updated On</t>
-  </si>
-  <si>
-    <t>10,063 km</t>
-  </si>
-  <si>
-    <t>$400.00</t>
-  </si>
-  <si>
-    <t>Rotate &amp; Balance Wheels</t>
-  </si>
-  <si>
-    <t>Tyre Puncture</t>
-  </si>
-  <si>
-    <t>12,305 km</t>
-  </si>
-  <si>
-    <t>$200.00</t>
-  </si>
-  <si>
-    <t>5 May 2026</t>
-  </si>
-  <si>
-    <t>12306</t>
-  </si>
-  <si>
-    <t>${TC005.Last Odometer Reading}</t>
-  </si>
-  <si>
     <t>${TC007.Last Odometer Reading}</t>
   </si>
   <si>
-    <t>${TC005.New Odometer}</t>
-  </si>
-  <si>
     <t>${TC007.New Odometer}</t>
   </si>
   <si>
-    <t>${TC005.Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC005.Last Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC005.Reference Number}</t>
-  </si>
-  <si>
-    <t>${TC005.Odometer}</t>
-  </si>
-  <si>
     <t>${TC007.Reading Date}</t>
   </si>
   <si>
@@ -290,22 +374,64 @@
     <t>${TC007.Odometer}</t>
   </si>
   <si>
-    <t>REQ-660</t>
-  </si>
-  <si>
-    <t>12308</t>
-  </si>
-  <si>
-    <t>7 May 2026</t>
-  </si>
-  <si>
-    <t>12322</t>
-  </si>
-  <si>
-    <t>20 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-744</t>
+    <t>Comprehensive Insurance</t>
+  </si>
+  <si>
+    <t>CTP</t>
+  </si>
+  <si>
+    <t>$500.00</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>Windscreen Repair</t>
+  </si>
+  <si>
+    <t>12368</t>
+  </si>
+  <si>
+    <t>REQ-818</t>
+  </si>
+  <si>
+    <t>12369</t>
+  </si>
+  <si>
+    <t>REQ-819</t>
+  </si>
+  <si>
+    <t>12370</t>
+  </si>
+  <si>
+    <t>REQ-820</t>
+  </si>
+  <si>
+    <t>12382</t>
+  </si>
+  <si>
+    <t>23 May 2026</t>
+  </si>
+  <si>
+    <t>REQ-833</t>
+  </si>
+  <si>
+    <t>12383</t>
+  </si>
+  <si>
+    <t>REQ-834</t>
+  </si>
+  <si>
+    <t>12384</t>
+  </si>
+  <si>
+    <t>REQ-835</t>
+  </si>
+  <si>
+    <t>12385</t>
+  </si>
+  <si>
+    <t>REQ-836</t>
   </si>
 </sst>
 </file>
@@ -315,40 +441,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -360,16 +458,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -413,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -421,7 +525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -433,31 +537,24 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,36 +851,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD10"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AY9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.5546875"/>
-    <col min="2" max="2" customWidth="true" width="20.6640625"/>
-    <col min="3" max="4" customWidth="true" width="24.33203125"/>
-    <col min="5" max="5" customWidth="true" width="27.33203125"/>
-    <col min="6" max="6" customWidth="true" width="16.77734375"/>
-    <col min="7" max="7" customWidth="true" width="15.33203125"/>
-    <col min="8" max="8" customWidth="true" width="21.77734375"/>
-    <col min="9" max="9" customWidth="true" width="18.6640625"/>
-    <col min="10" max="10" customWidth="true" width="23.77734375"/>
-    <col min="11" max="11" customWidth="true" width="17.21875"/>
-    <col min="12" max="12" customWidth="true" width="19.88671875"/>
-    <col min="13" max="13" customWidth="true" width="20.6640625"/>
-    <col min="14" max="14" customWidth="true" width="17.5546875"/>
-    <col min="15" max="15" customWidth="true" width="14.6640625"/>
-    <col min="16" max="16" customWidth="true" width="19.33203125"/>
-    <col min="17" max="17" customWidth="true" width="18.44140625"/>
-    <col min="18" max="22" customWidth="true" width="19.109375"/>
-    <col min="23" max="23" customWidth="true" width="25.6640625"/>
-    <col min="24" max="24" customWidth="true" style="9" width="27.109375"/>
-    <col min="25" max="25" customWidth="true" width="25.33203125"/>
-    <col min="26" max="26" customWidth="true" width="19.5546875"/>
-    <col min="27" max="27" customWidth="true" width="14.5546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="9" width="17.21875"/>
-    <col min="29" max="29" customWidth="true" style="9" width="15.109375"/>
+    <col min="1" max="1" customWidth="true" width="8.5"/>
+    <col min="2" max="2" customWidth="true" width="20.625"/>
+    <col min="3" max="4" customWidth="true" width="24.375"/>
+    <col min="5" max="5" customWidth="true" width="27.375"/>
+    <col min="6" max="6" customWidth="true" width="16.75"/>
+    <col min="7" max="7" customWidth="true" width="15.375"/>
+    <col min="8" max="8" customWidth="true" width="21.75"/>
+    <col min="9" max="9" customWidth="true" width="18.625"/>
+    <col min="10" max="10" customWidth="true" width="23.75"/>
+    <col min="11" max="11" customWidth="true" width="17.25"/>
+    <col min="12" max="12" customWidth="true" width="19.875"/>
+    <col min="13" max="13" customWidth="true" width="20.625"/>
+    <col min="14" max="14" customWidth="true" width="17.5"/>
+    <col min="15" max="15" customWidth="true" width="14.625"/>
+    <col min="16" max="16" customWidth="true" width="19.375"/>
+    <col min="17" max="17" customWidth="true" width="18.5"/>
+    <col min="18" max="22" customWidth="true" width="19.125"/>
+    <col min="23" max="23" customWidth="true" width="25.625"/>
+    <col min="24" max="24" customWidth="true" style="7" width="27.125"/>
+    <col min="25" max="25" customWidth="true" width="25.375"/>
+    <col min="26" max="26" customWidth="true" width="19.5"/>
+    <col min="27" max="27" customWidth="true" width="14.5"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="7" width="17.25"/>
+    <col min="29" max="29" customWidth="true" style="7" width="15.125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="1" customFormat="1" ht="60">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -851,29 +948,94 @@
         <v>21</v>
       </c>
       <c r="W1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="AA1" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AB1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AD1" s="14"/>
+      <c r="AI1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AX1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY1" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" s="2" customFormat="1" ht="75">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -881,30 +1043,30 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="D2" s="5" t="n">
         <f>C2+1</f>
-        <v>12309.0</v>
+        <v>12383.0</v>
       </c>
       <c r="E2" s="5" t="n">
         <f>C2+1</f>
-        <v>12309.0</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="11">
-        <v>600</v>
+        <v>12383.0</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>56</v>
+      <c r="J2" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
@@ -931,29 +1093,67 @@
         <v>24</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="V2" s="6" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,309 km</v>
+        <v>12,383 km</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
+      <c r="Y2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="11"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="11"/>
+      <c r="AS2" s="11"/>
+      <c r="AT2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" s="2" customFormat="1" ht="75">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -967,20 +1167,20 @@
       <c r="E3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="11">
-        <v>600</v>
+      <c r="F3" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>56</v>
+      <c r="J3" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
@@ -1019,49 +1219,115 @@
         <v>31</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
+      <c r="AD3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ3" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL3" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO3" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX3" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY3" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" s="2" customFormat="1" ht="75">
       <c r="A4" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="D4" s="5" t="n">
         <f>C4+1</f>
-        <v>12304.0</v>
+        <v>12384.0</v>
       </c>
       <c r="E4" s="5" t="n">
         <f>C4+1</f>
-        <v>12304.0</v>
+        <v>12384.0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="11">
-        <v>500</v>
+        <v>114</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>24</v>
@@ -1094,50 +1360,84 @@
         <v>24</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="V4" s="6" t="str">
         <f>TEXT(E4,"#,##0")&amp;" km"</f>
-        <v>12,304 km</v>
+        <v>12,384 km</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
+      <c r="Y4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX4" s="12"/>
+      <c r="AY4" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" s="2" customFormat="1" ht="67.5">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>66</v>
+        <v>114</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>24</v>
@@ -1170,65 +1470,127 @@
         <v>24</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="V5" s="13" t="s">
-        <v>65</v>
+        <v>90</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO5" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV5" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX5" s="12"/>
+      <c r="AY5" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="D6" s="5" t="n">
         <f>C6+1</f>
-        <v>12302.0</v>
+        <v>12385.0</v>
       </c>
       <c r="E6" s="5" t="n">
         <f>C6+1</f>
-        <v>12302.0</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1000</v>
+        <v>12385.0</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>24</v>
@@ -1261,50 +1623,88 @@
         <v>24</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="V6" s="6" t="str">
         <f>TEXT(E6,"#,##0")&amp;" km"</f>
-        <v>12,302 km</v>
+        <v>12,385 km</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
+      <c r="Y6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="4"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV6" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="11">
-        <v>1000</v>
+        <v>55</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>24</v>
@@ -1337,61 +1737,127 @@
         <v>24</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
+      <c r="AD7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL7" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO7" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU7" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV7" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW7" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY7" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="D8" s="5" t="n">
         <f>C8+1</f>
-        <v>12323.0</v>
+        <v>12386.0</v>
       </c>
       <c r="E8" s="5" t="n">
         <f>C8+1</f>
-        <v>12323.0</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="4">
-        <v>200</v>
+        <v>12386.0</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>24</v>
@@ -1424,53 +1890,88 @@
         <v>24</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>69</v>
+        <v>132</v>
+      </c>
+      <c r="V8" s="6" t="str">
+        <f>TEXT(E8,"#,##0")&amp;" km"</f>
+        <v>12,386 km</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="11"/>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
+      <c r="AT8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV8" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX8" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY8" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>24</v>
@@ -1503,40 +2004,104 @@
         <v>24</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="U10" s="7"/>
+      <c r="AD9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT9" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU9" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX9" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY9" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/03_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/03_NovatedApp_Regression.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86072938-7D03-4068-9FE3-CE000B372C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C22B1D-EA2F-4F82-B83A-7ED9C5903F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="136">
   <si>
     <t>TC ID</t>
   </si>
@@ -140,9 +140,6 @@
     <t>End Of Lease Date</t>
   </si>
   <si>
-    <t>30/08/2029 10:00 GMT+10:00</t>
-  </si>
-  <si>
     <t>Submitted By</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
     <t>$1,000.00</t>
   </si>
   <si>
-    <t>22 May 2026</t>
-  </si>
-  <si>
     <t>Mr</t>
   </si>
   <si>
@@ -323,30 +317,12 @@
     <t>The new australia insurance</t>
   </si>
   <si>
-    <t>12350</t>
-  </si>
-  <si>
-    <t>REQ-800</t>
-  </si>
-  <si>
     <t xml:space="preserve">Copy of CTP Renewal </t>
   </si>
   <si>
-    <t>12353</t>
-  </si>
-  <si>
-    <t>REQ-803</t>
-  </si>
-  <si>
     <t>$2,000.00</t>
   </si>
   <si>
-    <t>12355</t>
-  </si>
-  <si>
-    <t>REQ-805</t>
-  </si>
-  <si>
     <t>Claim type other has been raised due to some spare damage.</t>
   </si>
   <si>
@@ -389,49 +365,82 @@
     <t>Windscreen Repair</t>
   </si>
   <si>
-    <t>12368</t>
-  </si>
-  <si>
-    <t>REQ-818</t>
-  </si>
-  <si>
-    <t>12369</t>
-  </si>
-  <si>
-    <t>REQ-819</t>
-  </si>
-  <si>
-    <t>12370</t>
-  </si>
-  <si>
-    <t>REQ-820</t>
-  </si>
-  <si>
-    <t>12382</t>
-  </si>
-  <si>
-    <t>23 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-833</t>
-  </si>
-  <si>
-    <t>12383</t>
-  </si>
-  <si>
-    <t>REQ-834</t>
-  </si>
-  <si>
-    <t>12384</t>
-  </si>
-  <si>
-    <t>REQ-835</t>
-  </si>
-  <si>
-    <t>12385</t>
-  </si>
-  <si>
-    <t>REQ-836</t>
+    <t>30 Aug 2029</t>
+  </si>
+  <si>
+    <t>5569</t>
+  </si>
+  <si>
+    <t>2 Jun 2026</t>
+  </si>
+  <si>
+    <t>REQ-934</t>
+  </si>
+  <si>
+    <t>5570</t>
+  </si>
+  <si>
+    <t>REQ-935</t>
+  </si>
+  <si>
+    <t>5571</t>
+  </si>
+  <si>
+    <t>REQ-936</t>
+  </si>
+  <si>
+    <t>5572</t>
+  </si>
+  <si>
+    <t>REQ-937</t>
+  </si>
+  <si>
+    <t>${TC001.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC003.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC005.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC007.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>5582</t>
+  </si>
+  <si>
+    <t>REQ-953</t>
+  </si>
+  <si>
+    <t>5583</t>
+  </si>
+  <si>
+    <t>REQ-954</t>
+  </si>
+  <si>
+    <t>5584</t>
+  </si>
+  <si>
+    <t>REQ-955</t>
+  </si>
+  <si>
+    <t>5585</t>
+  </si>
+  <si>
+    <t>REQ-956</t>
+  </si>
+  <si>
+    <t>5586</t>
+  </si>
+  <si>
+    <t>REQ-957</t>
+  </si>
+  <si>
+    <t>5587</t>
+  </si>
+  <si>
+    <t>REQ-958</t>
   </si>
 </sst>
 </file>
@@ -954,67 +963,67 @@
         <v>34</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="AB1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AD1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AM1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AP1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="AR1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS1" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="AT1" s="9" t="s">
         <v>13</v>
@@ -1032,7 +1041,7 @@
         <v>16</v>
       </c>
       <c r="AY1" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:51" s="2" customFormat="1" ht="75">
@@ -1043,21 +1052,21 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D2" s="5" t="n">
         <f>C2+1</f>
-        <v>12383.0</v>
+        <v>5584.0</v>
       </c>
       <c r="E2" s="5" t="n">
         <f>C2+1</f>
-        <v>12383.0</v>
+        <v>5584.0</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>32</v>
@@ -1066,7 +1075,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
@@ -1093,27 +1102,29 @@
         <v>24</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V2" s="6" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,383 km</v>
+        <v>5,584 km</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X2" s="4"/>
+      <c r="X2" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="Y2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
@@ -1135,19 +1146,19 @@
       <c r="AR2" s="11"/>
       <c r="AS2" s="11"/>
       <c r="AT2" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AU2" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AV2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX2" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="AY2" s="12" t="s">
         <v>32</v>
@@ -1168,10 +1179,10 @@
         <v>27</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>32</v>
@@ -1180,7 +1191,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
@@ -1222,81 +1233,81 @@
         <v>32</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AG3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AH3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AI3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AH3" s="11" t="s">
+      <c r="AJ3" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AI3" s="4" t="s">
+      <c r="AK3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AJ3" s="11" t="s">
+      <c r="AL3" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AK3" s="4" t="s">
+      <c r="AM3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN3" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AL3" s="11" t="s">
+      <c r="AO3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AM3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN3" s="11" t="s">
+      <c r="AP3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AO3" s="11" t="s">
+      <c r="AR3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AP3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ3" s="11" t="s">
+      <c r="AV3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AR3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS3" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT3" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV3" s="12" t="s">
+      <c r="AX3" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="AW3" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX3" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="AY3" s="12" t="s">
         <v>32</v>
@@ -1304,27 +1315,27 @@
     </row>
     <row r="4" spans="1:51" s="2" customFormat="1" ht="75">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D4" s="5" t="n">
         <f>C4+1</f>
-        <v>12384.0</v>
+        <v>5588.0</v>
       </c>
       <c r="E4" s="5" t="n">
         <f>C4+1</f>
-        <v>12384.0</v>
+        <v>5588.0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>32</v>
@@ -1360,27 +1371,29 @@
         <v>24</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="V4" s="6" t="str">
         <f>TEXT(E4,"#,##0")&amp;" km"</f>
-        <v>12,384 km</v>
+        <v>5,588 km</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X4" s="4"/>
+      <c r="X4" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="Y4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
@@ -1403,13 +1416,13 @@
       <c r="AS4" s="11"/>
       <c r="AT4" s="11"/>
       <c r="AU4" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AV4" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AW4" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AX4" s="12"/>
       <c r="AY4" s="12" t="s">
@@ -1418,23 +1431,23 @@
     </row>
     <row r="5" spans="1:51" s="2" customFormat="1" ht="67.5">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>32</v>
@@ -1470,95 +1483,95 @@
         <v>24</v>
       </c>
       <c r="S5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="T5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="U5" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AD5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AG5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AH5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AG5" s="4" t="s">
+      <c r="AI5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AH5" s="11" t="s">
+      <c r="AJ5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AI5" s="4" t="s">
+      <c r="AK5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AJ5" s="11" t="s">
+      <c r="AL5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AK5" s="4" t="s">
+      <c r="AM5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN5" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AL5" s="11" t="s">
+      <c r="AO5" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AM5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN5" s="11" t="s">
+      <c r="AP5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ5" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="AR5" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AS5" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AT5" s="11"/>
       <c r="AU5" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AV5" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AW5" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AX5" s="12"/>
       <c r="AY5" s="4" t="s">
@@ -1567,27 +1580,27 @@
     </row>
     <row r="6" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D6" s="5" t="n">
         <f>C6+1</f>
-        <v>12385.0</v>
+        <v>5585.0</v>
       </c>
       <c r="E6" s="5" t="n">
         <f>C6+1</f>
-        <v>12385.0</v>
+        <v>5585.0</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>32</v>
@@ -1623,27 +1636,29 @@
         <v>24</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="V6" s="6" t="str">
         <f>TEXT(E6,"#,##0")&amp;" km"</f>
-        <v>12,385 km</v>
+        <v>5,585 km</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X6" s="4"/>
+      <c r="X6" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="Y6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
@@ -1665,19 +1680,19 @@
       <c r="AR6" s="11"/>
       <c r="AS6" s="11"/>
       <c r="AT6" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AU6" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AV6" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AW6" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AX6" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AY6" s="4" t="s">
         <v>32</v>
@@ -1685,148 +1700,148 @@
     </row>
     <row r="7" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="4" t="s">
+      <c r="T7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="V7" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="W7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AE7" s="4" t="s">
+      <c r="AG7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AF7" s="4" t="s">
+      <c r="AH7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AG7" s="4" t="s">
+      <c r="AI7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AH7" s="11" t="s">
+      <c r="AJ7" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AI7" s="4" t="s">
+      <c r="AK7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AJ7" s="11" t="s">
+      <c r="AL7" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AK7" s="4" t="s">
+      <c r="AM7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN7" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AL7" s="11" t="s">
+      <c r="AO7" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AM7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN7" s="11" t="s">
+      <c r="AP7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AO7" s="11" t="s">
+      <c r="AR7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU7" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AP7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ7" s="4" t="s">
+      <c r="AV7" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW7" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AR7" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS7" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT7" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU7" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV7" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW7" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="AX7" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AY7" s="4" t="s">
         <v>32</v>
@@ -1834,27 +1849,27 @@
     </row>
     <row r="8" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="n">
         <f>C8+1</f>
-        <v>12386.0</v>
+        <v>5586.0</v>
       </c>
       <c r="E8" s="5" t="n">
         <f>C8+1</f>
-        <v>12386.0</v>
+        <v>5586.0</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>32</v>
@@ -1890,27 +1905,29 @@
         <v>24</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V8" s="6" t="str">
         <f>TEXT(E8,"#,##0")&amp;" km"</f>
-        <v>12,386 km</v>
+        <v>5,586 km</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="X8" s="4"/>
+      <c r="X8" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="Y8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -1932,19 +1949,19 @@
       <c r="AR8" s="11"/>
       <c r="AS8" s="11"/>
       <c r="AT8" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AU8" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AV8" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AW8" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AX8" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AY8" s="4" t="s">
         <v>32</v>
@@ -1952,148 +1969,148 @@
     </row>
     <row r="9" spans="1:51" s="2" customFormat="1" ht="135">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="T9" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="W9" s="4" t="s">
         <v>32</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AE9" s="4" t="s">
+      <c r="AG9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AF9" s="4" t="s">
+      <c r="AH9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AG9" s="4" t="s">
+      <c r="AI9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AH9" s="11" t="s">
+      <c r="AJ9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AI9" s="4" t="s">
+      <c r="AK9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AJ9" s="11" t="s">
+      <c r="AL9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AK9" s="4" t="s">
+      <c r="AM9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AL9" s="11" t="s">
+      <c r="AO9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AM9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN9" s="11" t="s">
+      <c r="AP9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AO9" s="11" t="s">
+      <c r="AR9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU9" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AP9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ9" s="4" t="s">
+      <c r="AV9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW9" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AR9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS9" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU9" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV9" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW9" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="AX9" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AY9" s="4" t="s">
         <v>32</v>
